--- a/estudo-mercado-gtk/dossie-bnb/receitas-bnb.xlsx
+++ b/estudo-mercado-gtk/dossie-bnb/receitas-bnb.xlsx
@@ -750,22 +750,22 @@
         <v>522655</v>
       </c>
       <c r="F11" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="G11" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H11" s="13" t="n">
         <v>0.7175</v>
       </c>
-      <c r="G11" s="12" t="n">
+      <c r="I11" s="12" t="n">
         <v>375000</v>
       </c>
-      <c r="H11" s="13" t="n">
+      <c r="J11" s="13" t="n">
         <v>0.8929</v>
       </c>
-      <c r="I11" s="12" t="n">
+      <c r="K11" s="12" t="n">
         <v>466666.67</v>
-      </c>
-      <c r="J11" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="K11" s="12" t="n">
-        <v>522654.55</v>
       </c>
       <c r="L11" s="13" t="n">
         <v>1</v>
@@ -843,22 +843,22 @@
         <v>276813</v>
       </c>
       <c r="F12" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="G12" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H12" s="13" t="n">
         <v>0.4415</v>
       </c>
-      <c r="G12" s="12" t="n">
+      <c r="I12" s="12" t="n">
         <v>122222.22</v>
       </c>
-      <c r="H12" s="13" t="n">
+      <c r="J12" s="13" t="n">
         <v>0.7109000000000001</v>
       </c>
-      <c r="I12" s="12" t="n">
+      <c r="K12" s="12" t="n">
         <v>196777.78</v>
-      </c>
-      <c r="J12" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="K12" s="12" t="n">
-        <v>276813.33</v>
       </c>
       <c r="L12" s="13" t="n">
         <v>1</v>
@@ -936,22 +936,22 @@
         <v>153996</v>
       </c>
       <c r="F13" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="G13" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H13" s="13" t="n">
         <v>0.7015</v>
       </c>
-      <c r="G13" s="12" t="n">
+      <c r="I13" s="12" t="n">
         <v>108035.71</v>
       </c>
-      <c r="H13" s="13" t="n">
+      <c r="J13" s="13" t="n">
         <v>0.8929</v>
       </c>
-      <c r="I13" s="12" t="n">
+      <c r="K13" s="12" t="n">
         <v>137500</v>
-      </c>
-      <c r="J13" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="K13" s="12" t="n">
-        <v>153996.43</v>
       </c>
       <c r="L13" s="13" t="n">
         <v>1</v>
@@ -1029,22 +1029,22 @@
         <v>34844</v>
       </c>
       <c r="F14" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="G14" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H14" s="13" t="n">
         <v>0.4305</v>
       </c>
-      <c r="G14" s="12" t="n">
+      <c r="I14" s="12" t="n">
         <v>15000</v>
       </c>
-      <c r="H14" s="13" t="n">
+      <c r="J14" s="13" t="n">
         <v>0.7031000000000001</v>
       </c>
-      <c r="I14" s="12" t="n">
+      <c r="K14" s="12" t="n">
         <v>24500</v>
-      </c>
-      <c r="J14" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="K14" s="12" t="n">
-        <v>34843.64</v>
       </c>
       <c r="L14" s="13" t="n">
         <v>1</v>
@@ -1122,22 +1122,22 @@
         <v>21013</v>
       </c>
       <c r="F15" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="G15" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H15" s="13" t="n">
         <v>0.4822</v>
       </c>
-      <c r="G15" s="12" t="n">
+      <c r="I15" s="12" t="n">
         <v>10131.58</v>
       </c>
-      <c r="H15" s="13" t="n">
+      <c r="J15" s="13" t="n">
         <v>0.7554000000000001</v>
       </c>
-      <c r="I15" s="12" t="n">
+      <c r="K15" s="12" t="n">
         <v>15872.81</v>
-      </c>
-      <c r="J15" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="K15" s="12" t="n">
-        <v>21013.16</v>
       </c>
       <c r="L15" s="13" t="n">
         <v>1</v>
@@ -1197,7 +1197,7 @@
     <row r="18">
       <c r="A18" s="14" t="inlineStr">
         <is>
-          <t>OBS: Empresa em implantação: Qtd. Atual = 0 (sem operação). Qtd. Projetada = plano de regime (ano 3+), limitado ao teto de EPP (LC 123/2006) de R$ 4,8 milhões — receita de estabilização R$ 4.791.000. % de Utilização por ano reflete o ramp-up e a migração do mix para produtos de maior valor (vedação -&gt; estrutural e paver). Detalhamento mensal do ano 1 em previsao-faturamento.xlsx.</t>
+          <t>OBS: Empresa em implantação: coluna Ano Atual zerada (sem operação); Qtd. Atual = 0. Qtd. Projetada = plano de regime (Ano 3 em diante), limitado ao teto de EPP da LC 123/2006 — receita de estabilização de R$ 4.791.000. O % de Utilização por ano reflete o ramp-up comercial e a migração do mix para produtos de maior valor. Abertura mensal do Ano 1 em previsao-faturamento.pdf.</t>
         </is>
       </c>
     </row>

--- a/estudo-mercado-gtk/dossie-bnb/receitas-bnb.xlsx
+++ b/estudo-mercado-gtk/dossie-bnb/receitas-bnb.xlsx
@@ -536,7 +536,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC18"/>
+  <dimension ref="A1:AC24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
@@ -747,7 +747,7 @@
         <v>0</v>
       </c>
       <c r="E11" s="12" t="n">
-        <v>522655</v>
+        <v>426371</v>
       </c>
       <c r="F11" s="13" t="n">
         <v>0</v>
@@ -756,70 +756,70 @@
         <v>0</v>
       </c>
       <c r="H11" s="13" t="n">
-        <v>0.7175</v>
+        <v>0.6668000000000001</v>
       </c>
       <c r="I11" s="12" t="n">
-        <v>375000</v>
+        <v>284313.66</v>
       </c>
       <c r="J11" s="13" t="n">
-        <v>0.8929</v>
+        <v>0.8491</v>
       </c>
       <c r="K11" s="12" t="n">
-        <v>466666.67</v>
+        <v>362021.74</v>
       </c>
       <c r="L11" s="13" t="n">
         <v>1</v>
       </c>
       <c r="M11" s="12" t="n">
-        <v>522654.55</v>
+        <v>426371.33</v>
       </c>
       <c r="N11" s="13" t="n">
         <v>1</v>
       </c>
       <c r="O11" s="12" t="n">
-        <v>522654.55</v>
+        <v>426371.33</v>
       </c>
       <c r="P11" s="13" t="n">
         <v>1</v>
       </c>
       <c r="Q11" s="12" t="n">
-        <v>522654.55</v>
+        <v>426371.33</v>
       </c>
       <c r="R11" s="13" t="n">
         <v>1</v>
       </c>
       <c r="S11" s="12" t="n">
-        <v>522654.55</v>
+        <v>426371.33</v>
       </c>
       <c r="T11" s="13" t="n">
         <v>1</v>
       </c>
       <c r="U11" s="12" t="n">
-        <v>522654.55</v>
+        <v>426371.33</v>
       </c>
       <c r="V11" s="13" t="n">
         <v>1</v>
       </c>
       <c r="W11" s="12" t="n">
-        <v>522654.55</v>
+        <v>426371.33</v>
       </c>
       <c r="X11" s="13" t="n">
         <v>1</v>
       </c>
       <c r="Y11" s="12" t="n">
-        <v>522654.55</v>
+        <v>426371.33</v>
       </c>
       <c r="Z11" s="13" t="n">
         <v>1</v>
       </c>
       <c r="AA11" s="12" t="n">
-        <v>522654.55</v>
+        <v>426371.33</v>
       </c>
       <c r="AB11" s="13" t="n">
         <v>1</v>
       </c>
       <c r="AC11" s="12" t="n">
-        <v>522654.55</v>
+        <v>426371.33</v>
       </c>
     </row>
     <row r="12" ht="28" customHeight="1">
@@ -840,7 +840,7 @@
         <v>0</v>
       </c>
       <c r="E12" s="12" t="n">
-        <v>276813</v>
+        <v>218601</v>
       </c>
       <c r="F12" s="13" t="n">
         <v>0</v>
@@ -849,76 +849,76 @@
         <v>0</v>
       </c>
       <c r="H12" s="13" t="n">
-        <v>0.4415</v>
+        <v>0.5806</v>
       </c>
       <c r="I12" s="12" t="n">
-        <v>122222.22</v>
+        <v>126910.72</v>
       </c>
       <c r="J12" s="13" t="n">
-        <v>0.7109000000000001</v>
+        <v>0.8068000000000001</v>
       </c>
       <c r="K12" s="12" t="n">
-        <v>196777.78</v>
+        <v>176368.76</v>
       </c>
       <c r="L12" s="13" t="n">
         <v>1</v>
       </c>
       <c r="M12" s="12" t="n">
-        <v>276813.33</v>
+        <v>218600.76</v>
       </c>
       <c r="N12" s="13" t="n">
         <v>1</v>
       </c>
       <c r="O12" s="12" t="n">
-        <v>276813.33</v>
+        <v>218600.76</v>
       </c>
       <c r="P12" s="13" t="n">
         <v>1</v>
       </c>
       <c r="Q12" s="12" t="n">
-        <v>276813.33</v>
+        <v>218600.76</v>
       </c>
       <c r="R12" s="13" t="n">
         <v>1</v>
       </c>
       <c r="S12" s="12" t="n">
-        <v>276813.33</v>
+        <v>218600.76</v>
       </c>
       <c r="T12" s="13" t="n">
         <v>1</v>
       </c>
       <c r="U12" s="12" t="n">
-        <v>276813.33</v>
+        <v>218600.76</v>
       </c>
       <c r="V12" s="13" t="n">
         <v>1</v>
       </c>
       <c r="W12" s="12" t="n">
-        <v>276813.33</v>
+        <v>218600.76</v>
       </c>
       <c r="X12" s="13" t="n">
         <v>1</v>
       </c>
       <c r="Y12" s="12" t="n">
-        <v>276813.33</v>
+        <v>218600.76</v>
       </c>
       <c r="Z12" s="13" t="n">
         <v>1</v>
       </c>
       <c r="AA12" s="12" t="n">
-        <v>276813.33</v>
+        <v>218600.76</v>
       </c>
       <c r="AB12" s="13" t="n">
         <v>1</v>
       </c>
       <c r="AC12" s="12" t="n">
-        <v>276813.33</v>
+        <v>218600.76</v>
       </c>
     </row>
     <row r="13" ht="28" customHeight="1">
       <c r="A13" s="10" t="inlineStr">
         <is>
-          <t>Bloco de concreto 9x19x39 - vedação</t>
+          <t>Canaleta de concreto 14x19x39</t>
         </is>
       </c>
       <c r="B13" s="11" t="inlineStr">
@@ -927,13 +927,13 @@
         </is>
       </c>
       <c r="C13" s="12" t="n">
-        <v>2.8</v>
+        <v>5</v>
       </c>
       <c r="D13" s="12" t="n">
         <v>0</v>
       </c>
       <c r="E13" s="12" t="n">
-        <v>153996</v>
+        <v>34042</v>
       </c>
       <c r="F13" s="13" t="n">
         <v>0</v>
@@ -942,76 +942,76 @@
         <v>0</v>
       </c>
       <c r="H13" s="13" t="n">
-        <v>0.7015</v>
+        <v>0.5313</v>
       </c>
       <c r="I13" s="12" t="n">
-        <v>108035.71</v>
+        <v>18087.19</v>
       </c>
       <c r="J13" s="13" t="n">
-        <v>0.8929</v>
+        <v>0.7827</v>
       </c>
       <c r="K13" s="12" t="n">
-        <v>137500</v>
+        <v>26644.06</v>
       </c>
       <c r="L13" s="13" t="n">
         <v>1</v>
       </c>
       <c r="M13" s="12" t="n">
-        <v>153996.43</v>
+        <v>34042.11</v>
       </c>
       <c r="N13" s="13" t="n">
         <v>1</v>
       </c>
       <c r="O13" s="12" t="n">
-        <v>153996.43</v>
+        <v>34042.11</v>
       </c>
       <c r="P13" s="13" t="n">
         <v>1</v>
       </c>
       <c r="Q13" s="12" t="n">
-        <v>153996.43</v>
+        <v>34042.11</v>
       </c>
       <c r="R13" s="13" t="n">
         <v>1</v>
       </c>
       <c r="S13" s="12" t="n">
-        <v>153996.43</v>
+        <v>34042.11</v>
       </c>
       <c r="T13" s="13" t="n">
         <v>1</v>
       </c>
       <c r="U13" s="12" t="n">
-        <v>153996.43</v>
+        <v>34042.11</v>
       </c>
       <c r="V13" s="13" t="n">
         <v>1</v>
       </c>
       <c r="W13" s="12" t="n">
-        <v>153996.43</v>
+        <v>34042.11</v>
       </c>
       <c r="X13" s="13" t="n">
         <v>1</v>
       </c>
       <c r="Y13" s="12" t="n">
-        <v>153996.43</v>
+        <v>34042.11</v>
       </c>
       <c r="Z13" s="13" t="n">
         <v>1</v>
       </c>
       <c r="AA13" s="12" t="n">
-        <v>153996.43</v>
+        <v>34042.11</v>
       </c>
       <c r="AB13" s="13" t="n">
         <v>1</v>
       </c>
       <c r="AC13" s="12" t="n">
-        <v>153996.43</v>
+        <v>34042.11</v>
       </c>
     </row>
     <row r="14" ht="28" customHeight="1">
       <c r="A14" s="10" t="inlineStr">
         <is>
-          <t>Bloco 19x19x39 e canaletas</t>
+          <t>Bloco de concreto 9x19x39 - vedação</t>
         </is>
       </c>
       <c r="B14" s="11" t="inlineStr">
@@ -1020,13 +1020,13 @@
         </is>
       </c>
       <c r="C14" s="12" t="n">
-        <v>5.5</v>
+        <v>2.8</v>
       </c>
       <c r="D14" s="12" t="n">
         <v>0</v>
       </c>
       <c r="E14" s="12" t="n">
-        <v>34844</v>
+        <v>223337</v>
       </c>
       <c r="F14" s="13" t="n">
         <v>0</v>
@@ -1035,167 +1035,725 @@
         <v>0</v>
       </c>
       <c r="H14" s="13" t="n">
-        <v>0.4305</v>
+        <v>0.6668000000000001</v>
       </c>
       <c r="I14" s="12" t="n">
-        <v>15000</v>
+        <v>148926.2</v>
       </c>
       <c r="J14" s="13" t="n">
-        <v>0.7031000000000001</v>
+        <v>0.8491</v>
       </c>
       <c r="K14" s="12" t="n">
-        <v>24500</v>
+        <v>189630.44</v>
       </c>
       <c r="L14" s="13" t="n">
         <v>1</v>
       </c>
       <c r="M14" s="12" t="n">
-        <v>34843.64</v>
+        <v>223337.36</v>
       </c>
       <c r="N14" s="13" t="n">
         <v>1</v>
       </c>
       <c r="O14" s="12" t="n">
-        <v>34843.64</v>
+        <v>223337.36</v>
       </c>
       <c r="P14" s="13" t="n">
         <v>1</v>
       </c>
       <c r="Q14" s="12" t="n">
-        <v>34843.64</v>
+        <v>223337.36</v>
       </c>
       <c r="R14" s="13" t="n">
         <v>1</v>
       </c>
       <c r="S14" s="12" t="n">
-        <v>34843.64</v>
+        <v>223337.36</v>
       </c>
       <c r="T14" s="13" t="n">
         <v>1</v>
       </c>
       <c r="U14" s="12" t="n">
-        <v>34843.64</v>
+        <v>223337.36</v>
       </c>
       <c r="V14" s="13" t="n">
         <v>1</v>
       </c>
       <c r="W14" s="12" t="n">
-        <v>34843.64</v>
+        <v>223337.36</v>
       </c>
       <c r="X14" s="13" t="n">
         <v>1</v>
       </c>
       <c r="Y14" s="12" t="n">
-        <v>34843.64</v>
+        <v>223337.36</v>
       </c>
       <c r="Z14" s="13" t="n">
         <v>1</v>
       </c>
       <c r="AA14" s="12" t="n">
-        <v>34843.64</v>
+        <v>223337.36</v>
       </c>
       <c r="AB14" s="13" t="n">
         <v>1</v>
       </c>
       <c r="AC14" s="12" t="n">
-        <v>34843.64</v>
+        <v>223337.36</v>
       </c>
     </row>
     <row r="15" ht="28" customHeight="1">
       <c r="A15" s="10" t="inlineStr">
         <is>
-          <t>Piso intertravado (paver) 35 MPa</t>
+          <t>Bloco de concreto 9x19x39 - estrutural</t>
         </is>
       </c>
       <c r="B15" s="11" t="inlineStr">
         <is>
+          <t>UND</t>
+        </is>
+      </c>
+      <c r="C15" s="12" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="D15" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="E15" s="12" t="n">
+        <v>23422</v>
+      </c>
+      <c r="F15" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="G15" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H15" s="13" t="n">
+        <v>0.5805</v>
+      </c>
+      <c r="I15" s="12" t="n">
+        <v>13597.58</v>
+      </c>
+      <c r="J15" s="13" t="n">
+        <v>0.8068000000000001</v>
+      </c>
+      <c r="K15" s="12" t="n">
+        <v>18896.65</v>
+      </c>
+      <c r="L15" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="M15" s="12" t="n">
+        <v>23421.51</v>
+      </c>
+      <c r="N15" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="O15" s="12" t="n">
+        <v>23421.51</v>
+      </c>
+      <c r="P15" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q15" s="12" t="n">
+        <v>23421.51</v>
+      </c>
+      <c r="R15" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="S15" s="12" t="n">
+        <v>23421.51</v>
+      </c>
+      <c r="T15" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="U15" s="12" t="n">
+        <v>23421.51</v>
+      </c>
+      <c r="V15" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="W15" s="12" t="n">
+        <v>23421.51</v>
+      </c>
+      <c r="X15" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y15" s="12" t="n">
+        <v>23421.51</v>
+      </c>
+      <c r="Z15" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA15" s="12" t="n">
+        <v>23421.51</v>
+      </c>
+      <c r="AB15" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC15" s="12" t="n">
+        <v>23421.51</v>
+      </c>
+    </row>
+    <row r="16" ht="28" customHeight="1">
+      <c r="A16" s="10" t="inlineStr">
+        <is>
+          <t>Canaleta de concreto 9x19x39</t>
+        </is>
+      </c>
+      <c r="B16" s="11" t="inlineStr">
+        <is>
+          <t>UND</t>
+        </is>
+      </c>
+      <c r="C16" s="12" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="D16" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="E16" s="12" t="n">
+        <v>7860</v>
+      </c>
+      <c r="F16" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="G16" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H16" s="13" t="n">
+        <v>0.5313</v>
+      </c>
+      <c r="I16" s="12" t="n">
+        <v>4176.33</v>
+      </c>
+      <c r="J16" s="13" t="n">
+        <v>0.7827</v>
+      </c>
+      <c r="K16" s="12" t="n">
+        <v>6152.12</v>
+      </c>
+      <c r="L16" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="M16" s="12" t="n">
+        <v>7860.33</v>
+      </c>
+      <c r="N16" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="O16" s="12" t="n">
+        <v>7860.33</v>
+      </c>
+      <c r="P16" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q16" s="12" t="n">
+        <v>7860.33</v>
+      </c>
+      <c r="R16" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="S16" s="12" t="n">
+        <v>7860.33</v>
+      </c>
+      <c r="T16" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="U16" s="12" t="n">
+        <v>7860.33</v>
+      </c>
+      <c r="V16" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="W16" s="12" t="n">
+        <v>7860.33</v>
+      </c>
+      <c r="X16" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y16" s="12" t="n">
+        <v>7860.33</v>
+      </c>
+      <c r="Z16" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA16" s="12" t="n">
+        <v>7860.33</v>
+      </c>
+      <c r="AB16" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC16" s="12" t="n">
+        <v>7860.33</v>
+      </c>
+    </row>
+    <row r="17" ht="28" customHeight="1">
+      <c r="A17" s="10" t="inlineStr">
+        <is>
+          <t>Bloco de concreto 19x19x39 - vedação</t>
+        </is>
+      </c>
+      <c r="B17" s="11" t="inlineStr">
+        <is>
+          <t>UND</t>
+        </is>
+      </c>
+      <c r="C17" s="12" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="D17" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="E17" s="12" t="n">
+        <v>10152</v>
+      </c>
+      <c r="F17" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="G17" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H17" s="13" t="n">
+        <v>0.4743</v>
+      </c>
+      <c r="I17" s="12" t="n">
+        <v>4815.36</v>
+      </c>
+      <c r="J17" s="13" t="n">
+        <v>0.7547</v>
+      </c>
+      <c r="K17" s="12" t="n">
+        <v>7662.1</v>
+      </c>
+      <c r="L17" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="M17" s="12" t="n">
+        <v>10151.7</v>
+      </c>
+      <c r="N17" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="O17" s="12" t="n">
+        <v>10151.7</v>
+      </c>
+      <c r="P17" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q17" s="12" t="n">
+        <v>10151.7</v>
+      </c>
+      <c r="R17" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="S17" s="12" t="n">
+        <v>10151.7</v>
+      </c>
+      <c r="T17" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="U17" s="12" t="n">
+        <v>10151.7</v>
+      </c>
+      <c r="V17" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="W17" s="12" t="n">
+        <v>10151.7</v>
+      </c>
+      <c r="X17" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y17" s="12" t="n">
+        <v>10151.7</v>
+      </c>
+      <c r="Z17" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA17" s="12" t="n">
+        <v>10151.7</v>
+      </c>
+      <c r="AB17" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC17" s="12" t="n">
+        <v>10151.7</v>
+      </c>
+    </row>
+    <row r="18" ht="28" customHeight="1">
+      <c r="A18" s="10" t="inlineStr">
+        <is>
+          <t>Bloco de concreto 19x19x39 - estrutural</t>
+        </is>
+      </c>
+      <c r="B18" s="11" t="inlineStr">
+        <is>
+          <t>UND</t>
+        </is>
+      </c>
+      <c r="C18" s="12" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="D18" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="E18" s="12" t="n">
+        <v>40597</v>
+      </c>
+      <c r="F18" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="G18" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H18" s="13" t="n">
+        <v>0.4743</v>
+      </c>
+      <c r="I18" s="12" t="n">
+        <v>19256.93</v>
+      </c>
+      <c r="J18" s="13" t="n">
+        <v>0.7548</v>
+      </c>
+      <c r="K18" s="12" t="n">
+        <v>30641.22</v>
+      </c>
+      <c r="L18" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="M18" s="12" t="n">
+        <v>40597.28</v>
+      </c>
+      <c r="N18" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="O18" s="12" t="n">
+        <v>40597.28</v>
+      </c>
+      <c r="P18" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q18" s="12" t="n">
+        <v>40597.28</v>
+      </c>
+      <c r="R18" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="S18" s="12" t="n">
+        <v>40597.28</v>
+      </c>
+      <c r="T18" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="U18" s="12" t="n">
+        <v>40597.28</v>
+      </c>
+      <c r="V18" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="W18" s="12" t="n">
+        <v>40597.28</v>
+      </c>
+      <c r="X18" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y18" s="12" t="n">
+        <v>40597.28</v>
+      </c>
+      <c r="Z18" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA18" s="12" t="n">
+        <v>40597.28</v>
+      </c>
+      <c r="AB18" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC18" s="12" t="n">
+        <v>40597.28</v>
+      </c>
+    </row>
+    <row r="19" ht="28" customHeight="1">
+      <c r="A19" s="10" t="inlineStr">
+        <is>
+          <t>Canaleta de concreto 19x19x39</t>
+        </is>
+      </c>
+      <c r="B19" s="11" t="inlineStr">
+        <is>
+          <t>UND</t>
+        </is>
+      </c>
+      <c r="C19" s="12" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="D19" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="E19" s="12" t="n">
+        <v>4684</v>
+      </c>
+      <c r="F19" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="G19" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H19" s="13" t="n">
+        <v>0.4101</v>
+      </c>
+      <c r="I19" s="12" t="n">
+        <v>1920.7</v>
+      </c>
+      <c r="J19" s="13" t="n">
+        <v>0.7232999999999999</v>
+      </c>
+      <c r="K19" s="12" t="n">
+        <v>3387.91</v>
+      </c>
+      <c r="L19" s="13" t="n">
+        <v>1.0001</v>
+      </c>
+      <c r="M19" s="12" t="n">
+        <v>4684.3</v>
+      </c>
+      <c r="N19" s="13" t="n">
+        <v>1.0001</v>
+      </c>
+      <c r="O19" s="12" t="n">
+        <v>4684.3</v>
+      </c>
+      <c r="P19" s="13" t="n">
+        <v>1.0001</v>
+      </c>
+      <c r="Q19" s="12" t="n">
+        <v>4684.3</v>
+      </c>
+      <c r="R19" s="13" t="n">
+        <v>1.0001</v>
+      </c>
+      <c r="S19" s="12" t="n">
+        <v>4684.3</v>
+      </c>
+      <c r="T19" s="13" t="n">
+        <v>1.0001</v>
+      </c>
+      <c r="U19" s="12" t="n">
+        <v>4684.3</v>
+      </c>
+      <c r="V19" s="13" t="n">
+        <v>1.0001</v>
+      </c>
+      <c r="W19" s="12" t="n">
+        <v>4684.3</v>
+      </c>
+      <c r="X19" s="13" t="n">
+        <v>1.0001</v>
+      </c>
+      <c r="Y19" s="12" t="n">
+        <v>4684.3</v>
+      </c>
+      <c r="Z19" s="13" t="n">
+        <v>1.0001</v>
+      </c>
+      <c r="AA19" s="12" t="n">
+        <v>4684.3</v>
+      </c>
+      <c r="AB19" s="13" t="n">
+        <v>1.0001</v>
+      </c>
+      <c r="AC19" s="12" t="n">
+        <v>4684.3</v>
+      </c>
+    </row>
+    <row r="20" ht="28" customHeight="1">
+      <c r="A20" s="10" t="inlineStr">
+        <is>
+          <t>Piso intertravado (paver) 6 cm - 35 MPa</t>
+        </is>
+      </c>
+      <c r="B20" s="11" t="inlineStr">
+        <is>
           <t>M2</t>
         </is>
       </c>
-      <c r="C15" s="12" t="n">
+      <c r="C20" s="12" t="n">
         <v>57</v>
       </c>
-      <c r="D15" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="E15" s="12" t="n">
-        <v>21013</v>
-      </c>
-      <c r="F15" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="G15" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="H15" s="13" t="n">
-        <v>0.4822</v>
-      </c>
-      <c r="I15" s="12" t="n">
-        <v>10131.58</v>
-      </c>
-      <c r="J15" s="13" t="n">
-        <v>0.7554000000000001</v>
-      </c>
-      <c r="K15" s="12" t="n">
-        <v>15872.81</v>
-      </c>
-      <c r="L15" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="M15" s="12" t="n">
-        <v>21013.16</v>
-      </c>
-      <c r="N15" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="O15" s="12" t="n">
-        <v>21013.16</v>
-      </c>
-      <c r="P15" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q15" s="12" t="n">
-        <v>21013.16</v>
-      </c>
-      <c r="R15" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="S15" s="12" t="n">
-        <v>21013.16</v>
-      </c>
-      <c r="T15" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="U15" s="12" t="n">
-        <v>21013.16</v>
-      </c>
-      <c r="V15" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="W15" s="12" t="n">
-        <v>21013.16</v>
-      </c>
-      <c r="X15" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y15" s="12" t="n">
-        <v>21013.16</v>
-      </c>
-      <c r="Z15" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA15" s="12" t="n">
-        <v>21013.16</v>
-      </c>
-      <c r="AB15" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC15" s="12" t="n">
-        <v>21013.16</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="14" t="inlineStr">
+      <c r="D20" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="E20" s="12" t="n">
+        <v>6691</v>
+      </c>
+      <c r="F20" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="G20" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H20" s="13" t="n">
+        <v>0.5171</v>
+      </c>
+      <c r="I20" s="12" t="n">
+        <v>3459.83</v>
+      </c>
+      <c r="J20" s="13" t="n">
+        <v>0.7756999999999999</v>
+      </c>
+      <c r="K20" s="12" t="n">
+        <v>5190.43</v>
+      </c>
+      <c r="L20" s="13" t="n">
+        <v>1.0001</v>
+      </c>
+      <c r="M20" s="12" t="n">
+        <v>6691.34</v>
+      </c>
+      <c r="N20" s="13" t="n">
+        <v>1.0001</v>
+      </c>
+      <c r="O20" s="12" t="n">
+        <v>6691.34</v>
+      </c>
+      <c r="P20" s="13" t="n">
+        <v>1.0001</v>
+      </c>
+      <c r="Q20" s="12" t="n">
+        <v>6691.34</v>
+      </c>
+      <c r="R20" s="13" t="n">
+        <v>1.0001</v>
+      </c>
+      <c r="S20" s="12" t="n">
+        <v>6691.34</v>
+      </c>
+      <c r="T20" s="13" t="n">
+        <v>1.0001</v>
+      </c>
+      <c r="U20" s="12" t="n">
+        <v>6691.34</v>
+      </c>
+      <c r="V20" s="13" t="n">
+        <v>1.0001</v>
+      </c>
+      <c r="W20" s="12" t="n">
+        <v>6691.34</v>
+      </c>
+      <c r="X20" s="13" t="n">
+        <v>1.0001</v>
+      </c>
+      <c r="Y20" s="12" t="n">
+        <v>6691.34</v>
+      </c>
+      <c r="Z20" s="13" t="n">
+        <v>1.0001</v>
+      </c>
+      <c r="AA20" s="12" t="n">
+        <v>6691.34</v>
+      </c>
+      <c r="AB20" s="13" t="n">
+        <v>1.0001</v>
+      </c>
+      <c r="AC20" s="12" t="n">
+        <v>6691.34</v>
+      </c>
+    </row>
+    <row r="21" ht="28" customHeight="1">
+      <c r="A21" s="10" t="inlineStr">
+        <is>
+          <t>Piso intertravado (paver) 8 cm - 50 MPa</t>
+        </is>
+      </c>
+      <c r="B21" s="11" t="inlineStr">
+        <is>
+          <t>M2</t>
+        </is>
+      </c>
+      <c r="C21" s="12" t="n">
+        <v>78</v>
+      </c>
+      <c r="D21" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="E21" s="12" t="n">
+        <v>10466</v>
+      </c>
+      <c r="F21" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="G21" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H21" s="13" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="I21" s="12" t="n">
+        <v>4291.34</v>
+      </c>
+      <c r="J21" s="13" t="n">
+        <v>0.7232</v>
+      </c>
+      <c r="K21" s="12" t="n">
+        <v>7569.47</v>
+      </c>
+      <c r="L21" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="M21" s="12" t="n">
+        <v>10465.94</v>
+      </c>
+      <c r="N21" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="O21" s="12" t="n">
+        <v>10465.94</v>
+      </c>
+      <c r="P21" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q21" s="12" t="n">
+        <v>10465.94</v>
+      </c>
+      <c r="R21" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="S21" s="12" t="n">
+        <v>10465.94</v>
+      </c>
+      <c r="T21" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="U21" s="12" t="n">
+        <v>10465.94</v>
+      </c>
+      <c r="V21" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="W21" s="12" t="n">
+        <v>10465.94</v>
+      </c>
+      <c r="X21" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y21" s="12" t="n">
+        <v>10465.94</v>
+      </c>
+      <c r="Z21" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA21" s="12" t="n">
+        <v>10465.94</v>
+      </c>
+      <c r="AB21" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC21" s="12" t="n">
+        <v>10465.94</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="14" t="inlineStr">
         <is>
           <t>OBS: Empresa em implantação: coluna Ano Atual zerada (sem operação); Qtd. Atual = 0. Qtd. Projetada = plano de regime (Ano 3 em diante), limitado ao teto de EPP da LC 123/2006 — receita de estabilização de R$ 4.791.000. O % de Utilização por ano reflete o ramp-up comercial e a migração do mix para produtos de maior valor. Abertura mensal do Ano 1 em previsao-faturamento.pdf.</t>
         </is>
@@ -1208,13 +1766,13 @@
     <mergeCell ref="J10:K10"/>
     <mergeCell ref="P10:Q10"/>
     <mergeCell ref="R10:S10"/>
-    <mergeCell ref="A18:L18"/>
     <mergeCell ref="A1:AC1"/>
     <mergeCell ref="T10:U10"/>
     <mergeCell ref="V10:W10"/>
     <mergeCell ref="A7:AC7"/>
     <mergeCell ref="L10:M10"/>
     <mergeCell ref="N10:O10"/>
+    <mergeCell ref="A24:L24"/>
     <mergeCell ref="A5:AC5"/>
     <mergeCell ref="X10:Y10"/>
     <mergeCell ref="A8:AC8"/>

--- a/estudo-mercado-gtk/dossie-bnb/receitas-bnb.xlsx
+++ b/estudo-mercado-gtk/dossie-bnb/receitas-bnb.xlsx
@@ -741,13 +741,13 @@
         </is>
       </c>
       <c r="C11" s="12" t="n">
-        <v>3.3</v>
+        <v>3.43</v>
       </c>
       <c r="D11" s="12" t="n">
         <v>0</v>
       </c>
       <c r="E11" s="12" t="n">
-        <v>426371</v>
+        <v>420180</v>
       </c>
       <c r="F11" s="13" t="n">
         <v>0</v>
@@ -756,70 +756,70 @@
         <v>0</v>
       </c>
       <c r="H11" s="13" t="n">
-        <v>0.6668000000000001</v>
+        <v>0.6653</v>
       </c>
       <c r="I11" s="12" t="n">
-        <v>284313.66</v>
+        <v>279551.2</v>
       </c>
       <c r="J11" s="13" t="n">
-        <v>0.8491</v>
+        <v>0.8482999999999999</v>
       </c>
       <c r="K11" s="12" t="n">
-        <v>362021.74</v>
+        <v>356454.17</v>
       </c>
       <c r="L11" s="13" t="n">
         <v>1</v>
       </c>
       <c r="M11" s="12" t="n">
-        <v>426371.33</v>
+        <v>420179.95</v>
       </c>
       <c r="N11" s="13" t="n">
         <v>1</v>
       </c>
       <c r="O11" s="12" t="n">
-        <v>426371.33</v>
+        <v>420179.95</v>
       </c>
       <c r="P11" s="13" t="n">
         <v>1</v>
       </c>
       <c r="Q11" s="12" t="n">
-        <v>426371.33</v>
+        <v>420179.95</v>
       </c>
       <c r="R11" s="13" t="n">
         <v>1</v>
       </c>
       <c r="S11" s="12" t="n">
-        <v>426371.33</v>
+        <v>420179.95</v>
       </c>
       <c r="T11" s="13" t="n">
         <v>1</v>
       </c>
       <c r="U11" s="12" t="n">
-        <v>426371.33</v>
+        <v>420179.95</v>
       </c>
       <c r="V11" s="13" t="n">
         <v>1</v>
       </c>
       <c r="W11" s="12" t="n">
-        <v>426371.33</v>
+        <v>420179.95</v>
       </c>
       <c r="X11" s="13" t="n">
         <v>1</v>
       </c>
       <c r="Y11" s="12" t="n">
-        <v>426371.33</v>
+        <v>420179.95</v>
       </c>
       <c r="Z11" s="13" t="n">
         <v>1</v>
       </c>
       <c r="AA11" s="12" t="n">
-        <v>426371.33</v>
+        <v>420179.95</v>
       </c>
       <c r="AB11" s="13" t="n">
         <v>1</v>
       </c>
       <c r="AC11" s="12" t="n">
-        <v>426371.33</v>
+        <v>420179.95</v>
       </c>
     </row>
     <row r="12" ht="28" customHeight="1">
@@ -834,13 +834,13 @@
         </is>
       </c>
       <c r="C12" s="12" t="n">
-        <v>4.5</v>
+        <v>4.17</v>
       </c>
       <c r="D12" s="12" t="n">
         <v>0</v>
       </c>
       <c r="E12" s="12" t="n">
-        <v>218601</v>
+        <v>236623</v>
       </c>
       <c r="F12" s="13" t="n">
         <v>0</v>
@@ -849,70 +849,70 @@
         <v>0</v>
       </c>
       <c r="H12" s="13" t="n">
-        <v>0.5806</v>
+        <v>0.5792</v>
       </c>
       <c r="I12" s="12" t="n">
-        <v>126910.72</v>
+        <v>137063</v>
       </c>
       <c r="J12" s="13" t="n">
-        <v>0.8068000000000001</v>
+        <v>0.8062</v>
       </c>
       <c r="K12" s="12" t="n">
-        <v>176368.76</v>
+        <v>190757.1</v>
       </c>
       <c r="L12" s="13" t="n">
         <v>1</v>
       </c>
       <c r="M12" s="12" t="n">
-        <v>218600.76</v>
+        <v>236623.2</v>
       </c>
       <c r="N12" s="13" t="n">
         <v>1</v>
       </c>
       <c r="O12" s="12" t="n">
-        <v>218600.76</v>
+        <v>236623.2</v>
       </c>
       <c r="P12" s="13" t="n">
         <v>1</v>
       </c>
       <c r="Q12" s="12" t="n">
-        <v>218600.76</v>
+        <v>236623.2</v>
       </c>
       <c r="R12" s="13" t="n">
         <v>1</v>
       </c>
       <c r="S12" s="12" t="n">
-        <v>218600.76</v>
+        <v>236623.2</v>
       </c>
       <c r="T12" s="13" t="n">
         <v>1</v>
       </c>
       <c r="U12" s="12" t="n">
-        <v>218600.76</v>
+        <v>236623.2</v>
       </c>
       <c r="V12" s="13" t="n">
         <v>1</v>
       </c>
       <c r="W12" s="12" t="n">
-        <v>218600.76</v>
+        <v>236623.2</v>
       </c>
       <c r="X12" s="13" t="n">
         <v>1</v>
       </c>
       <c r="Y12" s="12" t="n">
-        <v>218600.76</v>
+        <v>236623.2</v>
       </c>
       <c r="Z12" s="13" t="n">
         <v>1</v>
       </c>
       <c r="AA12" s="12" t="n">
-        <v>218600.76</v>
+        <v>236623.2</v>
       </c>
       <c r="AB12" s="13" t="n">
         <v>1</v>
       </c>
       <c r="AC12" s="12" t="n">
-        <v>218600.76</v>
+        <v>236623.2</v>
       </c>
     </row>
     <row r="13" ht="28" customHeight="1">
@@ -927,13 +927,13 @@
         </is>
       </c>
       <c r="C13" s="12" t="n">
-        <v>5</v>
+        <v>4.41</v>
       </c>
       <c r="D13" s="12" t="n">
         <v>0</v>
       </c>
       <c r="E13" s="12" t="n">
-        <v>34042</v>
+        <v>35667</v>
       </c>
       <c r="F13" s="13" t="n">
         <v>0</v>
@@ -942,70 +942,70 @@
         <v>0</v>
       </c>
       <c r="H13" s="13" t="n">
-        <v>0.5313</v>
+        <v>0.5301</v>
       </c>
       <c r="I13" s="12" t="n">
-        <v>18087.19</v>
+        <v>18907.89</v>
       </c>
       <c r="J13" s="13" t="n">
-        <v>0.7827</v>
+        <v>0.7820999999999999</v>
       </c>
       <c r="K13" s="12" t="n">
-        <v>26644.06</v>
+        <v>27895.18</v>
       </c>
       <c r="L13" s="13" t="n">
         <v>1</v>
       </c>
       <c r="M13" s="12" t="n">
-        <v>34042.11</v>
+        <v>35667.46</v>
       </c>
       <c r="N13" s="13" t="n">
         <v>1</v>
       </c>
       <c r="O13" s="12" t="n">
-        <v>34042.11</v>
+        <v>35667.46</v>
       </c>
       <c r="P13" s="13" t="n">
         <v>1</v>
       </c>
       <c r="Q13" s="12" t="n">
-        <v>34042.11</v>
+        <v>35667.46</v>
       </c>
       <c r="R13" s="13" t="n">
         <v>1</v>
       </c>
       <c r="S13" s="12" t="n">
-        <v>34042.11</v>
+        <v>35667.46</v>
       </c>
       <c r="T13" s="13" t="n">
         <v>1</v>
       </c>
       <c r="U13" s="12" t="n">
-        <v>34042.11</v>
+        <v>35667.46</v>
       </c>
       <c r="V13" s="13" t="n">
         <v>1</v>
       </c>
       <c r="W13" s="12" t="n">
-        <v>34042.11</v>
+        <v>35667.46</v>
       </c>
       <c r="X13" s="13" t="n">
         <v>1</v>
       </c>
       <c r="Y13" s="12" t="n">
-        <v>34042.11</v>
+        <v>35667.46</v>
       </c>
       <c r="Z13" s="13" t="n">
         <v>1</v>
       </c>
       <c r="AA13" s="12" t="n">
-        <v>34042.11</v>
+        <v>35667.46</v>
       </c>
       <c r="AB13" s="13" t="n">
         <v>1</v>
       </c>
       <c r="AC13" s="12" t="n">
-        <v>34042.11</v>
+        <v>35667.46</v>
       </c>
     </row>
     <row r="14" ht="28" customHeight="1">
@@ -1020,13 +1020,13 @@
         </is>
       </c>
       <c r="C14" s="12" t="n">
-        <v>2.8</v>
+        <v>2.75</v>
       </c>
       <c r="D14" s="12" t="n">
         <v>0</v>
       </c>
       <c r="E14" s="12" t="n">
-        <v>223337</v>
+        <v>220094</v>
       </c>
       <c r="F14" s="13" t="n">
         <v>0</v>
@@ -1035,70 +1035,70 @@
         <v>0</v>
       </c>
       <c r="H14" s="13" t="n">
-        <v>0.6668000000000001</v>
+        <v>0.6653</v>
       </c>
       <c r="I14" s="12" t="n">
-        <v>148926.2</v>
+        <v>146431.58</v>
       </c>
       <c r="J14" s="13" t="n">
-        <v>0.8491</v>
+        <v>0.8482999999999999</v>
       </c>
       <c r="K14" s="12" t="n">
-        <v>189630.44</v>
+        <v>186714.09</v>
       </c>
       <c r="L14" s="13" t="n">
         <v>1</v>
       </c>
       <c r="M14" s="12" t="n">
-        <v>223337.36</v>
+        <v>220094.26</v>
       </c>
       <c r="N14" s="13" t="n">
         <v>1</v>
       </c>
       <c r="O14" s="12" t="n">
-        <v>223337.36</v>
+        <v>220094.26</v>
       </c>
       <c r="P14" s="13" t="n">
         <v>1</v>
       </c>
       <c r="Q14" s="12" t="n">
-        <v>223337.36</v>
+        <v>220094.26</v>
       </c>
       <c r="R14" s="13" t="n">
         <v>1</v>
       </c>
       <c r="S14" s="12" t="n">
-        <v>223337.36</v>
+        <v>220094.26</v>
       </c>
       <c r="T14" s="13" t="n">
         <v>1</v>
       </c>
       <c r="U14" s="12" t="n">
-        <v>223337.36</v>
+        <v>220094.26</v>
       </c>
       <c r="V14" s="13" t="n">
         <v>1</v>
       </c>
       <c r="W14" s="12" t="n">
-        <v>223337.36</v>
+        <v>220094.26</v>
       </c>
       <c r="X14" s="13" t="n">
         <v>1</v>
       </c>
       <c r="Y14" s="12" t="n">
-        <v>223337.36</v>
+        <v>220094.26</v>
       </c>
       <c r="Z14" s="13" t="n">
         <v>1</v>
       </c>
       <c r="AA14" s="12" t="n">
-        <v>223337.36</v>
+        <v>220094.26</v>
       </c>
       <c r="AB14" s="13" t="n">
         <v>1</v>
       </c>
       <c r="AC14" s="12" t="n">
-        <v>223337.36</v>
+        <v>220094.26</v>
       </c>
     </row>
     <row r="15" ht="28" customHeight="1">
@@ -1113,13 +1113,13 @@
         </is>
       </c>
       <c r="C15" s="12" t="n">
-        <v>3.4</v>
+        <v>2.72</v>
       </c>
       <c r="D15" s="12" t="n">
         <v>0</v>
       </c>
       <c r="E15" s="12" t="n">
-        <v>23422</v>
+        <v>25352</v>
       </c>
       <c r="F15" s="13" t="n">
         <v>0</v>
@@ -1128,70 +1128,70 @@
         <v>0</v>
       </c>
       <c r="H15" s="13" t="n">
-        <v>0.5805</v>
+        <v>0.5793</v>
       </c>
       <c r="I15" s="12" t="n">
-        <v>13597.58</v>
+        <v>14685.32</v>
       </c>
       <c r="J15" s="13" t="n">
-        <v>0.8068000000000001</v>
+        <v>0.8062</v>
       </c>
       <c r="K15" s="12" t="n">
-        <v>18896.65</v>
+        <v>20438.26</v>
       </c>
       <c r="L15" s="13" t="n">
         <v>1</v>
       </c>
       <c r="M15" s="12" t="n">
-        <v>23421.51</v>
+        <v>25352.49</v>
       </c>
       <c r="N15" s="13" t="n">
         <v>1</v>
       </c>
       <c r="O15" s="12" t="n">
-        <v>23421.51</v>
+        <v>25352.49</v>
       </c>
       <c r="P15" s="13" t="n">
         <v>1</v>
       </c>
       <c r="Q15" s="12" t="n">
-        <v>23421.51</v>
+        <v>25352.49</v>
       </c>
       <c r="R15" s="13" t="n">
         <v>1</v>
       </c>
       <c r="S15" s="12" t="n">
-        <v>23421.51</v>
+        <v>25352.49</v>
       </c>
       <c r="T15" s="13" t="n">
         <v>1</v>
       </c>
       <c r="U15" s="12" t="n">
-        <v>23421.51</v>
+        <v>25352.49</v>
       </c>
       <c r="V15" s="13" t="n">
         <v>1</v>
       </c>
       <c r="W15" s="12" t="n">
-        <v>23421.51</v>
+        <v>25352.49</v>
       </c>
       <c r="X15" s="13" t="n">
         <v>1</v>
       </c>
       <c r="Y15" s="12" t="n">
-        <v>23421.51</v>
+        <v>25352.49</v>
       </c>
       <c r="Z15" s="13" t="n">
         <v>1</v>
       </c>
       <c r="AA15" s="12" t="n">
-        <v>23421.51</v>
+        <v>25352.49</v>
       </c>
       <c r="AB15" s="13" t="n">
         <v>1</v>
       </c>
       <c r="AC15" s="12" t="n">
-        <v>23421.51</v>
+        <v>25352.49</v>
       </c>
     </row>
     <row r="16" ht="28" customHeight="1">
@@ -1206,13 +1206,13 @@
         </is>
       </c>
       <c r="C16" s="12" t="n">
-        <v>3.8</v>
+        <v>2.98</v>
       </c>
       <c r="D16" s="12" t="n">
         <v>0</v>
       </c>
       <c r="E16" s="12" t="n">
-        <v>7860</v>
+        <v>8049</v>
       </c>
       <c r="F16" s="13" t="n">
         <v>0</v>
@@ -1221,70 +1221,70 @@
         <v>0</v>
       </c>
       <c r="H16" s="13" t="n">
-        <v>0.5313</v>
+        <v>0.5301</v>
       </c>
       <c r="I16" s="12" t="n">
-        <v>4176.33</v>
+        <v>4266.9</v>
       </c>
       <c r="J16" s="13" t="n">
-        <v>0.7827</v>
+        <v>0.7820999999999999</v>
       </c>
       <c r="K16" s="12" t="n">
-        <v>6152.12</v>
+        <v>6295.04</v>
       </c>
       <c r="L16" s="13" t="n">
         <v>1</v>
       </c>
       <c r="M16" s="12" t="n">
-        <v>7860.33</v>
+        <v>8049</v>
       </c>
       <c r="N16" s="13" t="n">
         <v>1</v>
       </c>
       <c r="O16" s="12" t="n">
-        <v>7860.33</v>
+        <v>8049</v>
       </c>
       <c r="P16" s="13" t="n">
         <v>1</v>
       </c>
       <c r="Q16" s="12" t="n">
-        <v>7860.33</v>
+        <v>8049</v>
       </c>
       <c r="R16" s="13" t="n">
         <v>1</v>
       </c>
       <c r="S16" s="12" t="n">
-        <v>7860.33</v>
+        <v>8049</v>
       </c>
       <c r="T16" s="13" t="n">
         <v>1</v>
       </c>
       <c r="U16" s="12" t="n">
-        <v>7860.33</v>
+        <v>8049</v>
       </c>
       <c r="V16" s="13" t="n">
         <v>1</v>
       </c>
       <c r="W16" s="12" t="n">
-        <v>7860.33</v>
+        <v>8049</v>
       </c>
       <c r="X16" s="13" t="n">
         <v>1</v>
       </c>
       <c r="Y16" s="12" t="n">
-        <v>7860.33</v>
+        <v>8049</v>
       </c>
       <c r="Z16" s="13" t="n">
         <v>1</v>
       </c>
       <c r="AA16" s="12" t="n">
-        <v>7860.33</v>
+        <v>8049</v>
       </c>
       <c r="AB16" s="13" t="n">
         <v>1</v>
       </c>
       <c r="AC16" s="12" t="n">
-        <v>7860.33</v>
+        <v>8049</v>
       </c>
     </row>
     <row r="17" ht="28" customHeight="1">
@@ -1299,13 +1299,13 @@
         </is>
       </c>
       <c r="C17" s="12" t="n">
-        <v>4.4</v>
+        <v>4.26</v>
       </c>
       <c r="D17" s="12" t="n">
         <v>0</v>
       </c>
       <c r="E17" s="12" t="n">
-        <v>10152</v>
+        <v>10004</v>
       </c>
       <c r="F17" s="13" t="n">
         <v>0</v>
@@ -1314,70 +1314,70 @@
         <v>0</v>
       </c>
       <c r="H17" s="13" t="n">
-        <v>0.4743</v>
+        <v>0.4733</v>
       </c>
       <c r="I17" s="12" t="n">
-        <v>4815.36</v>
+        <v>4734.7</v>
       </c>
       <c r="J17" s="13" t="n">
-        <v>0.7547</v>
+        <v>0.7543000000000001</v>
       </c>
       <c r="K17" s="12" t="n">
-        <v>7662.1</v>
+        <v>7545.58</v>
       </c>
       <c r="L17" s="13" t="n">
         <v>1</v>
       </c>
       <c r="M17" s="12" t="n">
-        <v>10151.7</v>
+        <v>10004.28</v>
       </c>
       <c r="N17" s="13" t="n">
         <v>1</v>
       </c>
       <c r="O17" s="12" t="n">
-        <v>10151.7</v>
+        <v>10004.28</v>
       </c>
       <c r="P17" s="13" t="n">
         <v>1</v>
       </c>
       <c r="Q17" s="12" t="n">
-        <v>10151.7</v>
+        <v>10004.28</v>
       </c>
       <c r="R17" s="13" t="n">
         <v>1</v>
       </c>
       <c r="S17" s="12" t="n">
-        <v>10151.7</v>
+        <v>10004.28</v>
       </c>
       <c r="T17" s="13" t="n">
         <v>1</v>
       </c>
       <c r="U17" s="12" t="n">
-        <v>10151.7</v>
+        <v>10004.28</v>
       </c>
       <c r="V17" s="13" t="n">
         <v>1</v>
       </c>
       <c r="W17" s="12" t="n">
-        <v>10151.7</v>
+        <v>10004.28</v>
       </c>
       <c r="X17" s="13" t="n">
         <v>1</v>
       </c>
       <c r="Y17" s="12" t="n">
-        <v>10151.7</v>
+        <v>10004.28</v>
       </c>
       <c r="Z17" s="13" t="n">
         <v>1</v>
       </c>
       <c r="AA17" s="12" t="n">
-        <v>10151.7</v>
+        <v>10004.28</v>
       </c>
       <c r="AB17" s="13" t="n">
         <v>1</v>
       </c>
       <c r="AC17" s="12" t="n">
-        <v>10151.7</v>
+        <v>10004.28</v>
       </c>
     </row>
     <row r="18" ht="28" customHeight="1">
@@ -1392,13 +1392,13 @@
         </is>
       </c>
       <c r="C18" s="12" t="n">
-        <v>5.5</v>
+        <v>5.47</v>
       </c>
       <c r="D18" s="12" t="n">
         <v>0</v>
       </c>
       <c r="E18" s="12" t="n">
-        <v>40597</v>
+        <v>43944</v>
       </c>
       <c r="F18" s="13" t="n">
         <v>0</v>
@@ -1407,70 +1407,70 @@
         <v>0</v>
       </c>
       <c r="H18" s="13" t="n">
-        <v>0.4743</v>
+        <v>0.4733</v>
       </c>
       <c r="I18" s="12" t="n">
-        <v>19256.93</v>
+        <v>20797.39</v>
       </c>
       <c r="J18" s="13" t="n">
-        <v>0.7548</v>
+        <v>0.7542</v>
       </c>
       <c r="K18" s="12" t="n">
-        <v>30641.22</v>
+        <v>33144.31</v>
       </c>
       <c r="L18" s="13" t="n">
         <v>1</v>
       </c>
       <c r="M18" s="12" t="n">
-        <v>40597.28</v>
+        <v>43944.31</v>
       </c>
       <c r="N18" s="13" t="n">
         <v>1</v>
       </c>
       <c r="O18" s="12" t="n">
-        <v>40597.28</v>
+        <v>43944.31</v>
       </c>
       <c r="P18" s="13" t="n">
         <v>1</v>
       </c>
       <c r="Q18" s="12" t="n">
-        <v>40597.28</v>
+        <v>43944.31</v>
       </c>
       <c r="R18" s="13" t="n">
         <v>1</v>
       </c>
       <c r="S18" s="12" t="n">
-        <v>40597.28</v>
+        <v>43944.31</v>
       </c>
       <c r="T18" s="13" t="n">
         <v>1</v>
       </c>
       <c r="U18" s="12" t="n">
-        <v>40597.28</v>
+        <v>43944.31</v>
       </c>
       <c r="V18" s="13" t="n">
         <v>1</v>
       </c>
       <c r="W18" s="12" t="n">
-        <v>40597.28</v>
+        <v>43944.31</v>
       </c>
       <c r="X18" s="13" t="n">
         <v>1</v>
       </c>
       <c r="Y18" s="12" t="n">
-        <v>40597.28</v>
+        <v>43944.31</v>
       </c>
       <c r="Z18" s="13" t="n">
         <v>1</v>
       </c>
       <c r="AA18" s="12" t="n">
-        <v>40597.28</v>
+        <v>43944.31</v>
       </c>
       <c r="AB18" s="13" t="n">
         <v>1</v>
       </c>
       <c r="AC18" s="12" t="n">
-        <v>40597.28</v>
+        <v>43944.31</v>
       </c>
     </row>
     <row r="19" ht="28" customHeight="1">
@@ -1485,13 +1485,13 @@
         </is>
       </c>
       <c r="C19" s="12" t="n">
-        <v>6.3</v>
+        <v>5.29</v>
       </c>
       <c r="D19" s="12" t="n">
         <v>0</v>
       </c>
       <c r="E19" s="12" t="n">
-        <v>4684</v>
+        <v>5070</v>
       </c>
       <c r="F19" s="13" t="n">
         <v>0</v>
@@ -1500,70 +1500,70 @@
         <v>0</v>
       </c>
       <c r="H19" s="13" t="n">
-        <v>0.4101</v>
+        <v>0.4091</v>
       </c>
       <c r="I19" s="12" t="n">
-        <v>1920.7</v>
+        <v>2074.35</v>
       </c>
       <c r="J19" s="13" t="n">
-        <v>0.7232999999999999</v>
+        <v>0.7229000000000001</v>
       </c>
       <c r="K19" s="12" t="n">
-        <v>3387.91</v>
+        <v>3664.92</v>
       </c>
       <c r="L19" s="13" t="n">
         <v>1.0001</v>
       </c>
       <c r="M19" s="12" t="n">
-        <v>4684.3</v>
+        <v>5070.5</v>
       </c>
       <c r="N19" s="13" t="n">
         <v>1.0001</v>
       </c>
       <c r="O19" s="12" t="n">
-        <v>4684.3</v>
+        <v>5070.5</v>
       </c>
       <c r="P19" s="13" t="n">
         <v>1.0001</v>
       </c>
       <c r="Q19" s="12" t="n">
-        <v>4684.3</v>
+        <v>5070.5</v>
       </c>
       <c r="R19" s="13" t="n">
         <v>1.0001</v>
       </c>
       <c r="S19" s="12" t="n">
-        <v>4684.3</v>
+        <v>5070.5</v>
       </c>
       <c r="T19" s="13" t="n">
         <v>1.0001</v>
       </c>
       <c r="U19" s="12" t="n">
-        <v>4684.3</v>
+        <v>5070.5</v>
       </c>
       <c r="V19" s="13" t="n">
         <v>1.0001</v>
       </c>
       <c r="W19" s="12" t="n">
-        <v>4684.3</v>
+        <v>5070.5</v>
       </c>
       <c r="X19" s="13" t="n">
         <v>1.0001</v>
       </c>
       <c r="Y19" s="12" t="n">
-        <v>4684.3</v>
+        <v>5070.5</v>
       </c>
       <c r="Z19" s="13" t="n">
         <v>1.0001</v>
       </c>
       <c r="AA19" s="12" t="n">
-        <v>4684.3</v>
+        <v>5070.5</v>
       </c>
       <c r="AB19" s="13" t="n">
         <v>1.0001</v>
       </c>
       <c r="AC19" s="12" t="n">
-        <v>4684.3</v>
+        <v>5070.5</v>
       </c>
     </row>
     <row r="20" ht="28" customHeight="1">
@@ -1578,13 +1578,13 @@
         </is>
       </c>
       <c r="C20" s="12" t="n">
-        <v>57</v>
+        <v>57.73</v>
       </c>
       <c r="D20" s="12" t="n">
         <v>0</v>
       </c>
       <c r="E20" s="12" t="n">
-        <v>6691</v>
+        <v>7454</v>
       </c>
       <c r="F20" s="13" t="n">
         <v>0</v>
@@ -1593,70 +1593,70 @@
         <v>0</v>
       </c>
       <c r="H20" s="13" t="n">
-        <v>0.5171</v>
+        <v>0.5159</v>
       </c>
       <c r="I20" s="12" t="n">
-        <v>3459.83</v>
+        <v>3845.23</v>
       </c>
       <c r="J20" s="13" t="n">
-        <v>0.7756999999999999</v>
+        <v>0.7751</v>
       </c>
       <c r="K20" s="12" t="n">
-        <v>5190.43</v>
+        <v>5777.41</v>
       </c>
       <c r="L20" s="13" t="n">
-        <v>1.0001</v>
+        <v>0.9998999999999999</v>
       </c>
       <c r="M20" s="12" t="n">
-        <v>6691.34</v>
+        <v>7453.57</v>
       </c>
       <c r="N20" s="13" t="n">
-        <v>1.0001</v>
+        <v>0.9998999999999999</v>
       </c>
       <c r="O20" s="12" t="n">
-        <v>6691.34</v>
+        <v>7453.57</v>
       </c>
       <c r="P20" s="13" t="n">
-        <v>1.0001</v>
+        <v>0.9998999999999999</v>
       </c>
       <c r="Q20" s="12" t="n">
-        <v>6691.34</v>
+        <v>7453.57</v>
       </c>
       <c r="R20" s="13" t="n">
-        <v>1.0001</v>
+        <v>0.9998999999999999</v>
       </c>
       <c r="S20" s="12" t="n">
-        <v>6691.34</v>
+        <v>7453.57</v>
       </c>
       <c r="T20" s="13" t="n">
-        <v>1.0001</v>
+        <v>0.9998999999999999</v>
       </c>
       <c r="U20" s="12" t="n">
-        <v>6691.34</v>
+        <v>7453.57</v>
       </c>
       <c r="V20" s="13" t="n">
-        <v>1.0001</v>
+        <v>0.9998999999999999</v>
       </c>
       <c r="W20" s="12" t="n">
-        <v>6691.34</v>
+        <v>7453.57</v>
       </c>
       <c r="X20" s="13" t="n">
-        <v>1.0001</v>
+        <v>0.9998999999999999</v>
       </c>
       <c r="Y20" s="12" t="n">
-        <v>6691.34</v>
+        <v>7453.57</v>
       </c>
       <c r="Z20" s="13" t="n">
-        <v>1.0001</v>
+        <v>0.9998999999999999</v>
       </c>
       <c r="AA20" s="12" t="n">
-        <v>6691.34</v>
+        <v>7453.57</v>
       </c>
       <c r="AB20" s="13" t="n">
-        <v>1.0001</v>
+        <v>0.9998999999999999</v>
       </c>
       <c r="AC20" s="12" t="n">
-        <v>6691.34</v>
+        <v>7453.57</v>
       </c>
     </row>
     <row r="21" ht="28" customHeight="1">
@@ -1671,13 +1671,13 @@
         </is>
       </c>
       <c r="C21" s="12" t="n">
-        <v>78</v>
+        <v>65.83</v>
       </c>
       <c r="D21" s="12" t="n">
         <v>0</v>
       </c>
       <c r="E21" s="12" t="n">
-        <v>10466</v>
+        <v>11658</v>
       </c>
       <c r="F21" s="13" t="n">
         <v>0</v>
@@ -1686,70 +1686,70 @@
         <v>0</v>
       </c>
       <c r="H21" s="13" t="n">
-        <v>0.41</v>
+        <v>0.4091</v>
       </c>
       <c r="I21" s="12" t="n">
-        <v>4291.34</v>
+        <v>4769.36</v>
       </c>
       <c r="J21" s="13" t="n">
-        <v>0.7232</v>
+        <v>0.7228</v>
       </c>
       <c r="K21" s="12" t="n">
-        <v>7569.47</v>
+        <v>8426.42</v>
       </c>
       <c r="L21" s="13" t="n">
         <v>1</v>
       </c>
       <c r="M21" s="12" t="n">
-        <v>10465.94</v>
+        <v>11658.14</v>
       </c>
       <c r="N21" s="13" t="n">
         <v>1</v>
       </c>
       <c r="O21" s="12" t="n">
-        <v>10465.94</v>
+        <v>11658.14</v>
       </c>
       <c r="P21" s="13" t="n">
         <v>1</v>
       </c>
       <c r="Q21" s="12" t="n">
-        <v>10465.94</v>
+        <v>11658.14</v>
       </c>
       <c r="R21" s="13" t="n">
         <v>1</v>
       </c>
       <c r="S21" s="12" t="n">
-        <v>10465.94</v>
+        <v>11658.14</v>
       </c>
       <c r="T21" s="13" t="n">
         <v>1</v>
       </c>
       <c r="U21" s="12" t="n">
-        <v>10465.94</v>
+        <v>11658.14</v>
       </c>
       <c r="V21" s="13" t="n">
         <v>1</v>
       </c>
       <c r="W21" s="12" t="n">
-        <v>10465.94</v>
+        <v>11658.14</v>
       </c>
       <c r="X21" s="13" t="n">
         <v>1</v>
       </c>
       <c r="Y21" s="12" t="n">
-        <v>10465.94</v>
+        <v>11658.14</v>
       </c>
       <c r="Z21" s="13" t="n">
         <v>1</v>
       </c>
       <c r="AA21" s="12" t="n">
-        <v>10465.94</v>
+        <v>11658.14</v>
       </c>
       <c r="AB21" s="13" t="n">
         <v>1</v>
       </c>
       <c r="AC21" s="12" t="n">
-        <v>10465.94</v>
+        <v>11658.14</v>
       </c>
     </row>
     <row r="24">

--- a/estudo-mercado-gtk/dossie-bnb/receitas-bnb.xlsx
+++ b/estudo-mercado-gtk/dossie-bnb/receitas-bnb.xlsx
@@ -747,7 +747,7 @@
         <v>0</v>
       </c>
       <c r="E11" s="12" t="n">
-        <v>420180</v>
+        <v>441151</v>
       </c>
       <c r="F11" s="13" t="n">
         <v>0</v>
@@ -756,70 +756,70 @@
         <v>0</v>
       </c>
       <c r="H11" s="13" t="n">
-        <v>0.6653</v>
+        <v>0.6602</v>
       </c>
       <c r="I11" s="12" t="n">
-        <v>279551.2</v>
+        <v>291246.41</v>
       </c>
       <c r="J11" s="13" t="n">
-        <v>0.8482999999999999</v>
+        <v>0.8458</v>
       </c>
       <c r="K11" s="12" t="n">
-        <v>356454.17</v>
+        <v>373138.91</v>
       </c>
       <c r="L11" s="13" t="n">
         <v>1</v>
       </c>
       <c r="M11" s="12" t="n">
-        <v>420179.95</v>
+        <v>441151.4</v>
       </c>
       <c r="N11" s="13" t="n">
         <v>1</v>
       </c>
       <c r="O11" s="12" t="n">
-        <v>420179.95</v>
+        <v>441151.4</v>
       </c>
       <c r="P11" s="13" t="n">
         <v>1</v>
       </c>
       <c r="Q11" s="12" t="n">
-        <v>420179.95</v>
+        <v>441151.4</v>
       </c>
       <c r="R11" s="13" t="n">
         <v>1</v>
       </c>
       <c r="S11" s="12" t="n">
-        <v>420179.95</v>
+        <v>441151.4</v>
       </c>
       <c r="T11" s="13" t="n">
         <v>1</v>
       </c>
       <c r="U11" s="12" t="n">
-        <v>420179.95</v>
+        <v>441151.4</v>
       </c>
       <c r="V11" s="13" t="n">
         <v>1</v>
       </c>
       <c r="W11" s="12" t="n">
-        <v>420179.95</v>
+        <v>441151.4</v>
       </c>
       <c r="X11" s="13" t="n">
         <v>1</v>
       </c>
       <c r="Y11" s="12" t="n">
-        <v>420179.95</v>
+        <v>441151.4</v>
       </c>
       <c r="Z11" s="13" t="n">
         <v>1</v>
       </c>
       <c r="AA11" s="12" t="n">
-        <v>420179.95</v>
+        <v>441151.4</v>
       </c>
       <c r="AB11" s="13" t="n">
         <v>1</v>
       </c>
       <c r="AC11" s="12" t="n">
-        <v>420179.95</v>
+        <v>441151.4</v>
       </c>
     </row>
     <row r="12" ht="28" customHeight="1">
@@ -849,16 +849,16 @@
         <v>0</v>
       </c>
       <c r="H12" s="13" t="n">
-        <v>0.5792</v>
+        <v>0.5748</v>
       </c>
       <c r="I12" s="12" t="n">
-        <v>137063</v>
+        <v>136008.84</v>
       </c>
       <c r="J12" s="13" t="n">
-        <v>0.8062</v>
+        <v>0.804</v>
       </c>
       <c r="K12" s="12" t="n">
-        <v>190757.1</v>
+        <v>190240.56</v>
       </c>
       <c r="L12" s="13" t="n">
         <v>1</v>
@@ -933,7 +933,7 @@
         <v>0</v>
       </c>
       <c r="E13" s="12" t="n">
-        <v>35667</v>
+        <v>34940</v>
       </c>
       <c r="F13" s="13" t="n">
         <v>0</v>
@@ -942,70 +942,70 @@
         <v>0</v>
       </c>
       <c r="H13" s="13" t="n">
-        <v>0.5301</v>
+        <v>0.526</v>
       </c>
       <c r="I13" s="12" t="n">
-        <v>18907.89</v>
+        <v>18379.72</v>
       </c>
       <c r="J13" s="13" t="n">
-        <v>0.7820999999999999</v>
+        <v>0.7801</v>
       </c>
       <c r="K13" s="12" t="n">
-        <v>27895.18</v>
+        <v>27256.33</v>
       </c>
       <c r="L13" s="13" t="n">
         <v>1</v>
       </c>
       <c r="M13" s="12" t="n">
-        <v>35667.46</v>
+        <v>34939.87</v>
       </c>
       <c r="N13" s="13" t="n">
         <v>1</v>
       </c>
       <c r="O13" s="12" t="n">
-        <v>35667.46</v>
+        <v>34939.87</v>
       </c>
       <c r="P13" s="13" t="n">
         <v>1</v>
       </c>
       <c r="Q13" s="12" t="n">
-        <v>35667.46</v>
+        <v>34939.87</v>
       </c>
       <c r="R13" s="13" t="n">
         <v>1</v>
       </c>
       <c r="S13" s="12" t="n">
-        <v>35667.46</v>
+        <v>34939.87</v>
       </c>
       <c r="T13" s="13" t="n">
         <v>1</v>
       </c>
       <c r="U13" s="12" t="n">
-        <v>35667.46</v>
+        <v>34939.87</v>
       </c>
       <c r="V13" s="13" t="n">
         <v>1</v>
       </c>
       <c r="W13" s="12" t="n">
-        <v>35667.46</v>
+        <v>34939.87</v>
       </c>
       <c r="X13" s="13" t="n">
         <v>1</v>
       </c>
       <c r="Y13" s="12" t="n">
-        <v>35667.46</v>
+        <v>34939.87</v>
       </c>
       <c r="Z13" s="13" t="n">
         <v>1</v>
       </c>
       <c r="AA13" s="12" t="n">
-        <v>35667.46</v>
+        <v>34939.87</v>
       </c>
       <c r="AB13" s="13" t="n">
         <v>1</v>
       </c>
       <c r="AC13" s="12" t="n">
-        <v>35667.46</v>
+        <v>34939.87</v>
       </c>
     </row>
     <row r="14" ht="28" customHeight="1">
@@ -1026,7 +1026,7 @@
         <v>0</v>
       </c>
       <c r="E14" s="12" t="n">
-        <v>220094</v>
+        <v>199016</v>
       </c>
       <c r="F14" s="13" t="n">
         <v>0</v>
@@ -1035,70 +1035,70 @@
         <v>0</v>
       </c>
       <c r="H14" s="13" t="n">
-        <v>0.6653</v>
+        <v>0.6602</v>
       </c>
       <c r="I14" s="12" t="n">
-        <v>146431.58</v>
+        <v>131389.36</v>
       </c>
       <c r="J14" s="13" t="n">
-        <v>0.8482999999999999</v>
+        <v>0.8458</v>
       </c>
       <c r="K14" s="12" t="n">
-        <v>186714.09</v>
+        <v>168333.34</v>
       </c>
       <c r="L14" s="13" t="n">
         <v>1</v>
       </c>
       <c r="M14" s="12" t="n">
-        <v>220094.26</v>
+        <v>199015.67</v>
       </c>
       <c r="N14" s="13" t="n">
         <v>1</v>
       </c>
       <c r="O14" s="12" t="n">
-        <v>220094.26</v>
+        <v>199015.67</v>
       </c>
       <c r="P14" s="13" t="n">
         <v>1</v>
       </c>
       <c r="Q14" s="12" t="n">
-        <v>220094.26</v>
+        <v>199015.67</v>
       </c>
       <c r="R14" s="13" t="n">
         <v>1</v>
       </c>
       <c r="S14" s="12" t="n">
-        <v>220094.26</v>
+        <v>199015.67</v>
       </c>
       <c r="T14" s="13" t="n">
         <v>1</v>
       </c>
       <c r="U14" s="12" t="n">
-        <v>220094.26</v>
+        <v>199015.67</v>
       </c>
       <c r="V14" s="13" t="n">
         <v>1</v>
       </c>
       <c r="W14" s="12" t="n">
-        <v>220094.26</v>
+        <v>199015.67</v>
       </c>
       <c r="X14" s="13" t="n">
         <v>1</v>
       </c>
       <c r="Y14" s="12" t="n">
-        <v>220094.26</v>
+        <v>199015.67</v>
       </c>
       <c r="Z14" s="13" t="n">
         <v>1</v>
       </c>
       <c r="AA14" s="12" t="n">
-        <v>220094.26</v>
+        <v>199015.67</v>
       </c>
       <c r="AB14" s="13" t="n">
         <v>1</v>
       </c>
       <c r="AC14" s="12" t="n">
-        <v>220094.26</v>
+        <v>199015.67</v>
       </c>
     </row>
     <row r="15" ht="28" customHeight="1">
@@ -1128,16 +1128,16 @@
         <v>0</v>
       </c>
       <c r="H15" s="13" t="n">
-        <v>0.5793</v>
+        <v>0.5748</v>
       </c>
       <c r="I15" s="12" t="n">
-        <v>14685.32</v>
+        <v>14572.38</v>
       </c>
       <c r="J15" s="13" t="n">
-        <v>0.8062</v>
+        <v>0.804</v>
       </c>
       <c r="K15" s="12" t="n">
-        <v>20438.26</v>
+        <v>20382.92</v>
       </c>
       <c r="L15" s="13" t="n">
         <v>1</v>
@@ -1212,7 +1212,7 @@
         <v>0</v>
       </c>
       <c r="E16" s="12" t="n">
-        <v>8049</v>
+        <v>7361</v>
       </c>
       <c r="F16" s="13" t="n">
         <v>0</v>
@@ -1221,70 +1221,70 @@
         <v>0</v>
       </c>
       <c r="H16" s="13" t="n">
-        <v>0.5301</v>
+        <v>0.526</v>
       </c>
       <c r="I16" s="12" t="n">
-        <v>4266.9</v>
+        <v>3871.98</v>
       </c>
       <c r="J16" s="13" t="n">
-        <v>0.7820999999999999</v>
+        <v>0.7801</v>
       </c>
       <c r="K16" s="12" t="n">
-        <v>6295.04</v>
+        <v>5741.98</v>
       </c>
       <c r="L16" s="13" t="n">
         <v>1</v>
       </c>
       <c r="M16" s="12" t="n">
-        <v>8049</v>
+        <v>7360.64</v>
       </c>
       <c r="N16" s="13" t="n">
         <v>1</v>
       </c>
       <c r="O16" s="12" t="n">
-        <v>8049</v>
+        <v>7360.64</v>
       </c>
       <c r="P16" s="13" t="n">
         <v>1</v>
       </c>
       <c r="Q16" s="12" t="n">
-        <v>8049</v>
+        <v>7360.64</v>
       </c>
       <c r="R16" s="13" t="n">
         <v>1</v>
       </c>
       <c r="S16" s="12" t="n">
-        <v>8049</v>
+        <v>7360.64</v>
       </c>
       <c r="T16" s="13" t="n">
         <v>1</v>
       </c>
       <c r="U16" s="12" t="n">
-        <v>8049</v>
+        <v>7360.64</v>
       </c>
       <c r="V16" s="13" t="n">
         <v>1</v>
       </c>
       <c r="W16" s="12" t="n">
-        <v>8049</v>
+        <v>7360.64</v>
       </c>
       <c r="X16" s="13" t="n">
         <v>1</v>
       </c>
       <c r="Y16" s="12" t="n">
-        <v>8049</v>
+        <v>7360.64</v>
       </c>
       <c r="Z16" s="13" t="n">
         <v>1</v>
       </c>
       <c r="AA16" s="12" t="n">
-        <v>8049</v>
+        <v>7360.64</v>
       </c>
       <c r="AB16" s="13" t="n">
         <v>1</v>
       </c>
       <c r="AC16" s="12" t="n">
-        <v>8049</v>
+        <v>7360.64</v>
       </c>
     </row>
     <row r="17" ht="28" customHeight="1">
@@ -1305,7 +1305,7 @@
         <v>0</v>
       </c>
       <c r="E17" s="12" t="n">
-        <v>10004</v>
+        <v>7961</v>
       </c>
       <c r="F17" s="13" t="n">
         <v>0</v>
@@ -1314,70 +1314,70 @@
         <v>0</v>
       </c>
       <c r="H17" s="13" t="n">
-        <v>0.4733</v>
+        <v>0.4696</v>
       </c>
       <c r="I17" s="12" t="n">
-        <v>4734.7</v>
+        <v>3738.53</v>
       </c>
       <c r="J17" s="13" t="n">
-        <v>0.7543000000000001</v>
+        <v>0.7524</v>
       </c>
       <c r="K17" s="12" t="n">
-        <v>7545.58</v>
+        <v>5989.98</v>
       </c>
       <c r="L17" s="13" t="n">
         <v>1</v>
       </c>
       <c r="M17" s="12" t="n">
-        <v>10004.28</v>
+        <v>7960.63</v>
       </c>
       <c r="N17" s="13" t="n">
         <v>1</v>
       </c>
       <c r="O17" s="12" t="n">
-        <v>10004.28</v>
+        <v>7960.63</v>
       </c>
       <c r="P17" s="13" t="n">
         <v>1</v>
       </c>
       <c r="Q17" s="12" t="n">
-        <v>10004.28</v>
+        <v>7960.63</v>
       </c>
       <c r="R17" s="13" t="n">
         <v>1</v>
       </c>
       <c r="S17" s="12" t="n">
-        <v>10004.28</v>
+        <v>7960.63</v>
       </c>
       <c r="T17" s="13" t="n">
         <v>1</v>
       </c>
       <c r="U17" s="12" t="n">
-        <v>10004.28</v>
+        <v>7960.63</v>
       </c>
       <c r="V17" s="13" t="n">
         <v>1</v>
       </c>
       <c r="W17" s="12" t="n">
-        <v>10004.28</v>
+        <v>7960.63</v>
       </c>
       <c r="X17" s="13" t="n">
         <v>1</v>
       </c>
       <c r="Y17" s="12" t="n">
-        <v>10004.28</v>
+        <v>7960.63</v>
       </c>
       <c r="Z17" s="13" t="n">
         <v>1</v>
       </c>
       <c r="AA17" s="12" t="n">
-        <v>10004.28</v>
+        <v>7960.63</v>
       </c>
       <c r="AB17" s="13" t="n">
         <v>1</v>
       </c>
       <c r="AC17" s="12" t="n">
-        <v>10004.28</v>
+        <v>7960.63</v>
       </c>
     </row>
     <row r="18" ht="28" customHeight="1">
@@ -1407,16 +1407,16 @@
         <v>0</v>
       </c>
       <c r="H18" s="13" t="n">
-        <v>0.4733</v>
+        <v>0.4696</v>
       </c>
       <c r="I18" s="12" t="n">
-        <v>20797.39</v>
+        <v>20637.44</v>
       </c>
       <c r="J18" s="13" t="n">
-        <v>0.7542</v>
+        <v>0.7524999999999999</v>
       </c>
       <c r="K18" s="12" t="n">
-        <v>33144.31</v>
+        <v>33065.93</v>
       </c>
       <c r="L18" s="13" t="n">
         <v>1</v>
@@ -1500,16 +1500,16 @@
         <v>0</v>
       </c>
       <c r="H19" s="13" t="n">
-        <v>0.4091</v>
+        <v>0.406</v>
       </c>
       <c r="I19" s="12" t="n">
-        <v>2074.35</v>
+        <v>2058.39</v>
       </c>
       <c r="J19" s="13" t="n">
-        <v>0.7229000000000001</v>
+        <v>0.7212999999999999</v>
       </c>
       <c r="K19" s="12" t="n">
-        <v>3664.92</v>
+        <v>3657.1</v>
       </c>
       <c r="L19" s="13" t="n">
         <v>1.0001</v>
@@ -1584,7 +1584,7 @@
         <v>0</v>
       </c>
       <c r="E20" s="12" t="n">
-        <v>7454</v>
+        <v>10524</v>
       </c>
       <c r="F20" s="13" t="n">
         <v>0</v>
@@ -1593,70 +1593,70 @@
         <v>0</v>
       </c>
       <c r="H20" s="13" t="n">
-        <v>0.5159</v>
+        <v>0.5119</v>
       </c>
       <c r="I20" s="12" t="n">
-        <v>3845.23</v>
+        <v>5387.66</v>
       </c>
       <c r="J20" s="13" t="n">
-        <v>0.7751</v>
+        <v>0.7731999999999999</v>
       </c>
       <c r="K20" s="12" t="n">
-        <v>5777.41</v>
+        <v>8137.18</v>
       </c>
       <c r="L20" s="13" t="n">
-        <v>0.9998999999999999</v>
+        <v>1</v>
       </c>
       <c r="M20" s="12" t="n">
-        <v>7453.57</v>
+        <v>10524.36</v>
       </c>
       <c r="N20" s="13" t="n">
-        <v>0.9998999999999999</v>
+        <v>1</v>
       </c>
       <c r="O20" s="12" t="n">
-        <v>7453.57</v>
+        <v>10524.36</v>
       </c>
       <c r="P20" s="13" t="n">
-        <v>0.9998999999999999</v>
+        <v>1</v>
       </c>
       <c r="Q20" s="12" t="n">
-        <v>7453.57</v>
+        <v>10524.36</v>
       </c>
       <c r="R20" s="13" t="n">
-        <v>0.9998999999999999</v>
+        <v>1</v>
       </c>
       <c r="S20" s="12" t="n">
-        <v>7453.57</v>
+        <v>10524.36</v>
       </c>
       <c r="T20" s="13" t="n">
-        <v>0.9998999999999999</v>
+        <v>1</v>
       </c>
       <c r="U20" s="12" t="n">
-        <v>7453.57</v>
+        <v>10524.36</v>
       </c>
       <c r="V20" s="13" t="n">
-        <v>0.9998999999999999</v>
+        <v>1</v>
       </c>
       <c r="W20" s="12" t="n">
-        <v>7453.57</v>
+        <v>10524.36</v>
       </c>
       <c r="X20" s="13" t="n">
-        <v>0.9998999999999999</v>
+        <v>1</v>
       </c>
       <c r="Y20" s="12" t="n">
-        <v>7453.57</v>
+        <v>10524.36</v>
       </c>
       <c r="Z20" s="13" t="n">
-        <v>0.9998999999999999</v>
+        <v>1</v>
       </c>
       <c r="AA20" s="12" t="n">
-        <v>7453.57</v>
+        <v>10524.36</v>
       </c>
       <c r="AB20" s="13" t="n">
-        <v>0.9998999999999999</v>
+        <v>1</v>
       </c>
       <c r="AC20" s="12" t="n">
-        <v>7453.57</v>
+        <v>10524.36</v>
       </c>
     </row>
     <row r="21" ht="28" customHeight="1">
@@ -1677,7 +1677,7 @@
         <v>0</v>
       </c>
       <c r="E21" s="12" t="n">
-        <v>11658</v>
+        <v>8965</v>
       </c>
       <c r="F21" s="13" t="n">
         <v>0</v>
@@ -1686,70 +1686,70 @@
         <v>0</v>
       </c>
       <c r="H21" s="13" t="n">
-        <v>0.4091</v>
+        <v>0.406</v>
       </c>
       <c r="I21" s="12" t="n">
-        <v>4769.36</v>
+        <v>3639.46</v>
       </c>
       <c r="J21" s="13" t="n">
-        <v>0.7228</v>
+        <v>0.7212999999999999</v>
       </c>
       <c r="K21" s="12" t="n">
-        <v>8426.42</v>
+        <v>6466.16</v>
       </c>
       <c r="L21" s="13" t="n">
         <v>1</v>
       </c>
       <c r="M21" s="12" t="n">
-        <v>11658.14</v>
+        <v>8965.190000000001</v>
       </c>
       <c r="N21" s="13" t="n">
         <v>1</v>
       </c>
       <c r="O21" s="12" t="n">
-        <v>11658.14</v>
+        <v>8965.190000000001</v>
       </c>
       <c r="P21" s="13" t="n">
         <v>1</v>
       </c>
       <c r="Q21" s="12" t="n">
-        <v>11658.14</v>
+        <v>8965.190000000001</v>
       </c>
       <c r="R21" s="13" t="n">
         <v>1</v>
       </c>
       <c r="S21" s="12" t="n">
-        <v>11658.14</v>
+        <v>8965.190000000001</v>
       </c>
       <c r="T21" s="13" t="n">
         <v>1</v>
       </c>
       <c r="U21" s="12" t="n">
-        <v>11658.14</v>
+        <v>8965.190000000001</v>
       </c>
       <c r="V21" s="13" t="n">
         <v>1</v>
       </c>
       <c r="W21" s="12" t="n">
-        <v>11658.14</v>
+        <v>8965.190000000001</v>
       </c>
       <c r="X21" s="13" t="n">
         <v>1</v>
       </c>
       <c r="Y21" s="12" t="n">
-        <v>11658.14</v>
+        <v>8965.190000000001</v>
       </c>
       <c r="Z21" s="13" t="n">
         <v>1</v>
       </c>
       <c r="AA21" s="12" t="n">
-        <v>11658.14</v>
+        <v>8965.190000000001</v>
       </c>
       <c r="AB21" s="13" t="n">
         <v>1</v>
       </c>
       <c r="AC21" s="12" t="n">
-        <v>11658.14</v>
+        <v>8965.190000000001</v>
       </c>
     </row>
     <row r="24">
